--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10211"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengpin.ge\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\hydgn\BHPSbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lawrenceiu/Desktop/eps-us-3.4.7 working_D0228_T1015_woking/eps-us-3.4.7 HK working/InputData/hydgn/BHPSbP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{3B5B2FDD-1C1D-4007-8ACA-03FA5C3A99DC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="45" xr10:uidLastSave="{4F0C9096-B2D1-4BDE-96CA-961197C2A61F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F08FA7E-EDB6-AD43-BED5-FB69CA584EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10995" yWindow="1080" windowWidth="15645" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25820" windowHeight="11980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>BHPSbP BAU Hydrogen Production Shares by Pathway</t>
   </si>
@@ -92,20 +97,17 @@
   </si>
   <si>
     <t>Production Share (dimensionless)</t>
-  </si>
-  <si>
-    <t>HK has no plan on hydrogen, so use international one</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -113,7 +115,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -121,8 +123,15 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -159,8 +168,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -439,17 +448,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -457,67 +466,62 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>0.02</v>
       </c>
@@ -525,7 +529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>0.76</v>
       </c>
@@ -533,7 +537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24">
         <f>0.22</f>
         <v>0.22</v>
@@ -543,9 +547,10 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B19" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -557,555 +562,498 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="1" max="1" width="30.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="2">
+      <c r="B1" s="2">
         <v>2017</v>
       </c>
-      <c r="D1">
+      <c r="C1">
         <v>2018</v>
       </c>
-      <c r="E1" s="2">
+      <c r="D1" s="2">
         <v>2019</v>
       </c>
-      <c r="F1">
+      <c r="E1">
         <v>2020</v>
       </c>
-      <c r="G1" s="2">
+      <c r="F1" s="2">
         <v>2021</v>
       </c>
-      <c r="H1">
+      <c r="G1">
         <v>2022</v>
       </c>
-      <c r="I1" s="2">
+      <c r="H1" s="2">
         <v>2023</v>
       </c>
-      <c r="J1">
+      <c r="I1">
         <v>2024</v>
       </c>
-      <c r="K1" s="2">
+      <c r="J1" s="2">
         <v>2025</v>
       </c>
-      <c r="L1">
+      <c r="K1">
         <v>2026</v>
       </c>
-      <c r="M1" s="2">
+      <c r="L1" s="2">
         <v>2027</v>
       </c>
-      <c r="N1">
+      <c r="M1">
         <v>2028</v>
       </c>
-      <c r="O1" s="2">
+      <c r="N1" s="2">
         <v>2029</v>
       </c>
-      <c r="P1">
+      <c r="O1">
         <v>2030</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="P1" s="2">
         <v>2031</v>
       </c>
-      <c r="R1">
+      <c r="Q1">
         <v>2032</v>
       </c>
-      <c r="S1" s="2">
+      <c r="R1" s="2">
         <v>2033</v>
       </c>
-      <c r="T1">
+      <c r="S1">
         <v>2034</v>
       </c>
-      <c r="U1" s="2">
+      <c r="T1" s="2">
         <v>2035</v>
       </c>
-      <c r="V1">
+      <c r="U1">
         <v>2036</v>
       </c>
-      <c r="W1" s="2">
+      <c r="V1" s="2">
         <v>2037</v>
       </c>
-      <c r="X1">
+      <c r="W1">
         <v>2038</v>
       </c>
-      <c r="Y1" s="2">
+      <c r="X1" s="2">
         <v>2039</v>
       </c>
-      <c r="Z1">
+      <c r="Y1">
         <v>2040</v>
       </c>
-      <c r="AA1" s="2">
+      <c r="Z1" s="2">
         <v>2041</v>
       </c>
-      <c r="AB1">
+      <c r="AA1">
         <v>2042</v>
       </c>
-      <c r="AC1" s="2">
+      <c r="AB1" s="2">
         <v>2043</v>
       </c>
-      <c r="AD1">
+      <c r="AC1">
         <v>2044</v>
       </c>
-      <c r="AE1" s="2">
+      <c r="AD1" s="2">
         <v>2045</v>
       </c>
-      <c r="AF1">
+      <c r="AE1">
         <v>2046</v>
       </c>
-      <c r="AG1" s="2">
+      <c r="AF1" s="2">
         <v>2047</v>
       </c>
-      <c r="AH1">
+      <c r="AG1">
         <v>2048</v>
       </c>
-      <c r="AI1" s="2">
+      <c r="AH1" s="2">
         <v>2049</v>
       </c>
-      <c r="AJ1">
+      <c r="AI1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.02</v>
+        <f>$B2</f>
+        <v>0</v>
       </c>
       <c r="D2">
-        <f>$C2</f>
-        <v>0.02</v>
+        <f t="shared" ref="D2:AI6" si="0">$B2</f>
+        <v>0</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:AJ6" si="0">$C2</f>
-        <v>0.02</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="R2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="S2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="T2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="U2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="V2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="W2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="X2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="AI2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="AJ2">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.76</v>
+        <f t="shared" ref="C3:R6" si="1">$B3</f>
+        <v>1</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:S6" si="1">$C3</f>
-        <v>0.76</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="N3">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="S3">
-        <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="T3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="U3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="V3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="W3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="X3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
-      </c>
-      <c r="AJ3">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <f>0.22</f>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f>0.22</f>
-        <v>0.22</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="1"/>
-        <v>0.22</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f t="shared" si="0"/>
-        <v>0.22</v>
-      </c>
-      <c r="AJ4">
-        <f t="shared" si="0"/>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1113,10 +1061,11 @@
         <v>0</v>
       </c>
       <c r="C5">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E5">
@@ -1243,12 +1192,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AJ5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1256,10 +1201,11 @@
         <v>0</v>
       </c>
       <c r="C6">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6">
@@ -1386,42 +1332,49 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AJ6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1429,24 +1382,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1465,70 +1479,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1630,34 +1597,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859B11A2-12A3-4602-8E35-0801755A5680}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A330DE4A-2A5F-4A2B-8D20-E1F83E2F84D3}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5D84DA1-2C59-4299-ABF0-55EA5DC3813C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -1666,30 +1622,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B33CC892-B349-42B0-A31D-69858F8470EB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D19A87E-1466-4452-8E04-C30623BC0338}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lawrenceiu/Desktop/eps-us-3.4.7 working_D0228_T1015_woking/eps-us-3.4.7 HK working/InputData/hydgn/BHPSbP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdeng\Desktop\Dropbox_Free_Zone\EPS\Model Repos\China\Subnational\eps-hongkong\InputData\hydgn\BHPSbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F08FA7E-EDB6-AD43-BED5-FB69CA584EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBB3D58-9983-4018-8132-FD3F481801D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25820" windowHeight="11980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2190" yWindow="1110" windowWidth="23595" windowHeight="12900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -115,7 +115,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -123,24 +123,36 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -156,7 +168,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -166,10 +178,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="超連結" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -447,10 +461,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.796875" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -486,63 +500,63 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
+      <c r="A13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>17</v>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="B17" t="s">
-        <v>12</v>
+      <c r="B16" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="B18" t="s">
-        <v>13</v>
+      <c r="A18" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="B19" s="4" t="s">
-        <v>14</v>
+      <c r="A19">
+        <v>0.02</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>0.76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>0.02</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>0.76</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
+      <c r="A21">
         <f>0.22</f>
         <v>0.22</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B21" t="s">
         <v>15</v>
       </c>
     </row>
@@ -550,7 +564,7 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B19" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -563,9 +577,9 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.19921875" customWidth="1"/>
+    <col min="1" max="1" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -730,67 +744,79 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="5">
         <v>0.1</v>
       </c>
-      <c r="P2">
-        <v>0.1</v>
-      </c>
-      <c r="Q2">
-        <v>0.1</v>
-      </c>
-      <c r="R2">
-        <v>0.1</v>
-      </c>
-      <c r="S2">
-        <v>0.1</v>
-      </c>
-      <c r="T2">
+      <c r="P2" s="6">
+        <f>($T2-$O2)/COUNT($P$1:$T$1)+O2</f>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="Q2" s="6">
+        <f t="shared" ref="Q2:S3" si="1">($T2-$O2)/COUNT($P$1:$T$1)+P2</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R2" s="6">
+        <f t="shared" si="1"/>
+        <v>0.16</v>
+      </c>
+      <c r="S2" s="6">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="T2" s="5">
         <v>0.2</v>
       </c>
-      <c r="U2">
-        <v>0.2</v>
-      </c>
-      <c r="V2">
-        <v>0.2</v>
-      </c>
-      <c r="W2">
-        <v>0.2</v>
-      </c>
-      <c r="X2">
-        <v>0.2</v>
-      </c>
-      <c r="Y2">
+      <c r="U2" s="6">
+        <f>($Y2-$T2)/COUNT($U$1:$Y$1)+T2</f>
+        <v>0.26</v>
+      </c>
+      <c r="V2" s="6">
+        <f t="shared" ref="V2:X3" si="2">($Y2-$T2)/COUNT($U$1:$Y$1)+U2</f>
+        <v>0.32</v>
+      </c>
+      <c r="W2" s="6">
+        <f t="shared" si="2"/>
+        <v>0.38</v>
+      </c>
+      <c r="X2" s="6">
+        <f t="shared" si="2"/>
+        <v>0.44</v>
+      </c>
+      <c r="Y2" s="5">
         <v>0.5</v>
       </c>
-      <c r="Z2">
-        <v>0.5</v>
-      </c>
-      <c r="AA2">
-        <v>0.5</v>
-      </c>
-      <c r="AB2">
-        <v>0.5</v>
-      </c>
-      <c r="AC2">
-        <v>0.5</v>
-      </c>
-      <c r="AD2">
+      <c r="Z2" s="6">
+        <f>($AD2-$Y2)/COUNT($Z$1:$AD$1)+Y2</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AA2" s="6">
+        <f t="shared" ref="AA2:AC3" si="3">($AD2-$Y2)/COUNT($Z$1:$AD$1)+Z2</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="AB2" s="6">
+        <f t="shared" si="3"/>
+        <v>0.68000000000000016</v>
+      </c>
+      <c r="AC2" s="6">
+        <f t="shared" si="3"/>
+        <v>0.74000000000000021</v>
+      </c>
+      <c r="AD2" s="5">
         <v>0.8</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="5">
         <v>0.8</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="5">
         <v>0.8</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="5">
         <v>0.8</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="5">
         <v>0.8</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="5">
         <v>0.8</v>
       </c>
     </row>
@@ -802,114 +828,126 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:R6" si="1">$B3</f>
+        <f t="shared" ref="C3:N6" si="4">$B3</f>
         <v>1</v>
       </c>
       <c r="D3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P3" s="6">
+        <f>($T3-$O3)/COUNT($P$1:$T$1)+O3</f>
+        <v>0.88</v>
+      </c>
+      <c r="Q3" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E3">
+        <v>0.86</v>
+      </c>
+      <c r="R3" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="F3">
+        <v>0.84</v>
+      </c>
+      <c r="S3" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>0.9</v>
-      </c>
-      <c r="P3">
-        <v>0.9</v>
-      </c>
-      <c r="Q3">
-        <v>0.9</v>
-      </c>
-      <c r="R3">
-        <v>0.9</v>
-      </c>
-      <c r="S3">
-        <v>0.9</v>
-      </c>
-      <c r="T3">
+        <v>0.82</v>
+      </c>
+      <c r="T3" s="5">
         <v>0.8</v>
       </c>
-      <c r="U3">
-        <v>0.8</v>
-      </c>
-      <c r="V3">
-        <v>0.8</v>
-      </c>
-      <c r="W3">
-        <v>0.8</v>
-      </c>
-      <c r="X3">
-        <v>0.8</v>
-      </c>
-      <c r="Y3">
+      <c r="U3" s="6">
+        <f>($Y3-$T3)/COUNT($U$1:$Y$1)+T3</f>
+        <v>0.74</v>
+      </c>
+      <c r="V3" s="6">
+        <f t="shared" si="2"/>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="W3" s="6">
+        <f t="shared" si="2"/>
+        <v>0.61999999999999988</v>
+      </c>
+      <c r="X3" s="6">
+        <f t="shared" si="2"/>
+        <v>0.55999999999999983</v>
+      </c>
+      <c r="Y3" s="5">
         <v>0.5</v>
       </c>
-      <c r="Z3">
-        <v>0.5</v>
-      </c>
-      <c r="AA3">
-        <v>0.5</v>
-      </c>
-      <c r="AB3">
-        <v>0.5</v>
-      </c>
-      <c r="AC3">
-        <v>0.5</v>
-      </c>
-      <c r="AD3">
+      <c r="Z3" s="6">
+        <f>($AD3-$Y3)/COUNT($Z$1:$AD$1)+Y3</f>
+        <v>0.44</v>
+      </c>
+      <c r="AA3" s="6">
+        <f t="shared" si="3"/>
+        <v>0.38</v>
+      </c>
+      <c r="AB3" s="6">
+        <f t="shared" si="3"/>
+        <v>0.32</v>
+      </c>
+      <c r="AC3" s="6">
+        <f t="shared" si="3"/>
+        <v>0.26</v>
+      </c>
+      <c r="AD3" s="5">
         <v>0.2</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="5">
         <v>0.2</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="5">
         <v>0.2</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="5">
         <v>0.2</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="5">
         <v>0.2</v>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="5">
         <v>0.2</v>
       </c>
     </row>
@@ -921,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D4">
@@ -1061,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D5">
@@ -1201,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D6">
@@ -1340,15 +1378,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
     <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
@@ -1597,15 +1626,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859B11A2-12A3-4602-8E35-0801755A5680}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5D84DA1-2C59-4299-ABF0-55EA5DC3813C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1622,4 +1652,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859B11A2-12A3-4602-8E35-0801755A5680}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>